--- a/sulamericana/datasets_sula/3_classificacao_por_jogo_semi_sula.xlsx
+++ b/sulamericana/datasets_sula/3_classificacao_por_jogo_semi_sula.xlsx
@@ -50,10 +50,10 @@
     <t>Jogo 1 (JG1)</t>
   </si>
   <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
     <t>JUV. KP</t>
-  </si>
-  <si>
-    <t>JV5 Tricolor Gaúcho</t>
   </si>
   <si>
     <t>Jogo 2 (JG2)</t>
@@ -472,16 +472,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>80.52001953125</v>
+        <v>193.0703125</v>
       </c>
       <c r="H2">
-        <v>60.1201171875</v>
+        <v>177.6201171875</v>
       </c>
       <c r="I2">
-        <v>20.39990234375</v>
+        <v>15.4501953125</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -495,10 +495,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -507,13 +507,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>60.1201171875</v>
+        <v>177.6201171875</v>
       </c>
       <c r="H3">
-        <v>80.52001953125</v>
+        <v>193.0703125</v>
       </c>
       <c r="I3">
-        <v>-20.39990234375</v>
+        <v>-15.4501953125</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -569,10 +569,10 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -581,13 +581,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>85.72021484375</v>
+        <v>195.8203125</v>
       </c>
       <c r="H2">
-        <v>66.919921875</v>
+        <v>172.77001953125</v>
       </c>
       <c r="I2">
-        <v>18.80029296875</v>
+        <v>23.05029296875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -610,16 +610,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>66.919921875</v>
+        <v>172.77001953125</v>
       </c>
       <c r="H3">
-        <v>85.72021484375</v>
+        <v>195.8203125</v>
       </c>
       <c r="I3">
-        <v>-18.80029296875</v>
+        <v>-23.05029296875</v>
       </c>
       <c r="J3">
         <v>2</v>
